--- a/my EVE 2025-06-08.xlsx
+++ b/my EVE 2025-06-08.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="114">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -159,6 +159,15 @@
     <t xml:space="preserve">X alliance approoved</t>
   </si>
   <si>
+    <t xml:space="preserve">Gallentiada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wukelan.che</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wukelan.che@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Newa Matara</t>
   </si>
   <si>
@@ -172,9 +181,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ady Bee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gallentiada</t>
   </si>
   <si>
     <t xml:space="preserve">Gallenteria</t>
@@ -2222,9 +2228,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>966240</xdr:colOff>
+      <xdr:colOff>965880</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>178920</xdr:rowOff>
+      <xdr:rowOff>178560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2238,7 +2244,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6198840" y="4390920"/>
-          <a:ext cx="2046240" cy="893520"/>
+          <a:ext cx="2045880" cy="893160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2259,9 +2265,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>775440</xdr:colOff>
+      <xdr:colOff>775080</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>207720</xdr:rowOff>
+      <xdr:rowOff>207360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2275,7 +2281,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6198840" y="11772720"/>
-          <a:ext cx="1855440" cy="912600"/>
+          <a:ext cx="1855080" cy="912240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2296,9 +2302,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>796680</xdr:colOff>
+      <xdr:colOff>796320</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>189000</xdr:rowOff>
+      <xdr:rowOff>188640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2312,7 +2318,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6105600" y="6648480"/>
-          <a:ext cx="1969920" cy="903240"/>
+          <a:ext cx="1969560" cy="902880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2333,9 +2339,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>739440</xdr:colOff>
+      <xdr:colOff>739080</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>207720</xdr:rowOff>
+      <xdr:rowOff>207360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2349,7 +2355,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6105600" y="7601040"/>
-          <a:ext cx="1912680" cy="921960"/>
+          <a:ext cx="1912320" cy="921600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2370,9 +2376,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1165680</xdr:colOff>
+      <xdr:colOff>1165320</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>169560</xdr:rowOff>
+      <xdr:rowOff>169200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2386,7 +2392,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8545680" y="10801440"/>
-          <a:ext cx="2246040" cy="893520"/>
+          <a:ext cx="2245680" cy="893160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2407,9 +2413,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>508680</xdr:colOff>
+      <xdr:colOff>508320</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>188640</xdr:rowOff>
+      <xdr:rowOff>188280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2423,7 +2429,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8545680" y="11772720"/>
-          <a:ext cx="1589040" cy="893520"/>
+          <a:ext cx="1588680" cy="893160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2444,9 +2450,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>537120</xdr:colOff>
+      <xdr:colOff>536760</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>169560</xdr:rowOff>
+      <xdr:rowOff>169200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2460,7 +2466,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8526600" y="4381560"/>
-          <a:ext cx="1636560" cy="893520"/>
+          <a:ext cx="1636200" cy="893160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2481,9 +2487,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>482040</xdr:colOff>
+      <xdr:colOff>481680</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>179280</xdr:rowOff>
+      <xdr:rowOff>178920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2497,7 +2503,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="6648480"/>
-          <a:ext cx="1655640" cy="893520"/>
+          <a:ext cx="1655280" cy="893160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2518,9 +2524,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>529560</xdr:colOff>
+      <xdr:colOff>529200</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>207720</xdr:rowOff>
+      <xdr:rowOff>207360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2534,7 +2540,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="7601040"/>
-          <a:ext cx="1703160" cy="921960"/>
+          <a:ext cx="1702800" cy="921600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2555,9 +2561,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>891720</xdr:colOff>
+      <xdr:colOff>891360</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>189000</xdr:rowOff>
+      <xdr:rowOff>188640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2571,7 +2577,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6105600" y="8553600"/>
-          <a:ext cx="2064960" cy="903240"/>
+          <a:ext cx="2064600" cy="902880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2592,9 +2598,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>405720</xdr:colOff>
+      <xdr:colOff>405360</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>179280</xdr:rowOff>
+      <xdr:rowOff>178920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2608,7 +2614,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="8553600"/>
-          <a:ext cx="1579320" cy="893520"/>
+          <a:ext cx="1578960" cy="893160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2629,9 +2635,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1118520</xdr:colOff>
+      <xdr:colOff>1118160</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>198000</xdr:rowOff>
+      <xdr:rowOff>197640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2645,7 +2651,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6198840" y="10820160"/>
-          <a:ext cx="2198520" cy="903240"/>
+          <a:ext cx="2198160" cy="902880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2666,9 +2672,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>844200</xdr:colOff>
+      <xdr:colOff>843840</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>188640</xdr:rowOff>
+      <xdr:rowOff>188280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2682,7 +2688,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6105600" y="237960"/>
-          <a:ext cx="2017440" cy="903240"/>
+          <a:ext cx="2017080" cy="902880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2703,9 +2709,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1063080</xdr:colOff>
+      <xdr:colOff>1062720</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>169560</xdr:rowOff>
+      <xdr:rowOff>169200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2719,7 +2725,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="237960"/>
-          <a:ext cx="2236680" cy="884160"/>
+          <a:ext cx="2236320" cy="883800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2740,9 +2746,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>987120</xdr:colOff>
+      <xdr:colOff>986760</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>179280</xdr:rowOff>
+      <xdr:rowOff>178920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2756,7 +2762,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6105600" y="14621040"/>
-          <a:ext cx="2160360" cy="893520"/>
+          <a:ext cx="2160000" cy="893160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2777,9 +2783,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>529560</xdr:colOff>
+      <xdr:colOff>529200</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>189000</xdr:rowOff>
+      <xdr:rowOff>188640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2793,7 +2799,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="14621040"/>
-          <a:ext cx="1703160" cy="903240"/>
+          <a:ext cx="1702800" cy="902880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2814,9 +2820,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1090080</xdr:colOff>
+      <xdr:colOff>1089720</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>207720</xdr:rowOff>
+      <xdr:rowOff>207360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2830,7 +2836,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6198840" y="2495520"/>
-          <a:ext cx="2170080" cy="912600"/>
+          <a:ext cx="2169720" cy="912240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2851,9 +2857,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>784800</xdr:colOff>
+      <xdr:colOff>784440</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>188640</xdr:rowOff>
+      <xdr:rowOff>188280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2867,7 +2873,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8545680" y="2495520"/>
-          <a:ext cx="1865160" cy="893520"/>
+          <a:ext cx="1864800" cy="893160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2888,9 +2894,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1082520</xdr:colOff>
+      <xdr:colOff>1082160</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>169560</xdr:rowOff>
+      <xdr:rowOff>169200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2904,7 +2910,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6105600" y="15573240"/>
-          <a:ext cx="2255760" cy="884160"/>
+          <a:ext cx="2255400" cy="883800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2925,9 +2931,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>681840</xdr:colOff>
+      <xdr:colOff>681480</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>169560</xdr:rowOff>
+      <xdr:rowOff>169200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2941,7 +2947,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="15573240"/>
-          <a:ext cx="1855440" cy="884160"/>
+          <a:ext cx="1855080" cy="883800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2962,9 +2968,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>682200</xdr:colOff>
+      <xdr:colOff>681840</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>189000</xdr:rowOff>
+      <xdr:rowOff>188640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2978,7 +2984,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6105600" y="13668480"/>
-          <a:ext cx="1855440" cy="903240"/>
+          <a:ext cx="1855080" cy="902880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2999,9 +3005,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>758160</xdr:colOff>
+      <xdr:colOff>757800</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>169920</xdr:rowOff>
+      <xdr:rowOff>169560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3015,7 +3021,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="13668480"/>
-          <a:ext cx="1931760" cy="884160"/>
+          <a:ext cx="1931400" cy="883800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3036,9 +3042,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>337320</xdr:colOff>
+      <xdr:colOff>336960</xdr:colOff>
       <xdr:row>132</xdr:row>
-      <xdr:rowOff>180360</xdr:rowOff>
+      <xdr:rowOff>180000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3052,7 +3058,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="247680" y="26546040"/>
-          <a:ext cx="8542080" cy="5655960"/>
+          <a:ext cx="8541720" cy="5655600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3073,9 +3079,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>318240</xdr:colOff>
+      <xdr:colOff>317880</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>550440</xdr:rowOff>
+      <xdr:rowOff>550080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3089,7 +3095,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="5343480"/>
-          <a:ext cx="4333320" cy="1265040"/>
+          <a:ext cx="4332960" cy="1264680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3110,9 +3116,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>270360</xdr:colOff>
+      <xdr:colOff>270000</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>541080</xdr:rowOff>
+      <xdr:rowOff>540720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3126,7 +3132,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="1190520"/>
-          <a:ext cx="4285440" cy="1255680"/>
+          <a:ext cx="4285080" cy="1255320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3147,9 +3153,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>78120</xdr:colOff>
+      <xdr:colOff>77760</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>426600</xdr:rowOff>
+      <xdr:rowOff>426240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3163,7 +3169,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6198840" y="1190520"/>
-          <a:ext cx="2331720" cy="1141200"/>
+          <a:ext cx="2331360" cy="1140840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3184,9 +3190,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>23040</xdr:colOff>
+      <xdr:colOff>22680</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>426600</xdr:rowOff>
+      <xdr:rowOff>426240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3200,7 +3206,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6105600" y="5343480"/>
-          <a:ext cx="2369880" cy="1141200"/>
+          <a:ext cx="2369520" cy="1140840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3221,9 +3227,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>2234520</xdr:colOff>
+      <xdr:colOff>2234160</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>559800</xdr:rowOff>
+      <xdr:rowOff>559440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3237,7 +3243,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="9505800"/>
-          <a:ext cx="3408120" cy="1274400"/>
+          <a:ext cx="3407760" cy="1274040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3258,9 +3264,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>32760</xdr:colOff>
+      <xdr:colOff>32400</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>417240</xdr:rowOff>
+      <xdr:rowOff>416880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3274,7 +3280,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6105600" y="9505800"/>
-          <a:ext cx="2379600" cy="1131840"/>
+          <a:ext cx="2379240" cy="1131480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3295,9 +3301,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1531800</xdr:colOff>
+      <xdr:colOff>1531440</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3311,7 +3317,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9626040" y="27746280"/>
-          <a:ext cx="1531800" cy="150480"/>
+          <a:ext cx="1531440" cy="150120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3332,9 +3338,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1130040</xdr:colOff>
+      <xdr:colOff>1129680</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>283680</xdr:rowOff>
+      <xdr:rowOff>283320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3348,7 +3354,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6105600" y="16525800"/>
-          <a:ext cx="2303280" cy="998280"/>
+          <a:ext cx="2302920" cy="997920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3369,9 +3375,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>2225160</xdr:colOff>
+      <xdr:colOff>2224800</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>541080</xdr:rowOff>
+      <xdr:rowOff>540720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3385,7 +3391,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8452440" y="16525800"/>
-          <a:ext cx="3398760" cy="1255680"/>
+          <a:ext cx="3398400" cy="1255320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3406,9 +3412,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>91440</xdr:colOff>
+      <xdr:colOff>91080</xdr:colOff>
       <xdr:row>119</xdr:row>
-      <xdr:rowOff>66240</xdr:rowOff>
+      <xdr:rowOff>65880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3422,7 +3428,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8490600" y="27746280"/>
-          <a:ext cx="1226880" cy="1245960"/>
+          <a:ext cx="1226520" cy="1245600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3443,9 +3449,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>2720520</xdr:colOff>
+      <xdr:colOff>2720160</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>176400</xdr:rowOff>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3459,7 +3465,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8633520" y="26632080"/>
-          <a:ext cx="3713040" cy="636480"/>
+          <a:ext cx="3712680" cy="636120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3480,9 +3486,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>173520</xdr:colOff>
+      <xdr:colOff>173160</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>55080</xdr:rowOff>
+      <xdr:rowOff>54720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3496,7 +3502,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13474800" y="237960"/>
-          <a:ext cx="3551040" cy="4446360"/>
+          <a:ext cx="3550680" cy="4446000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3517,12 +3523,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AMJ1048576"/>
-  <sheetFormatPr defaultColWidth="12.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="12.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.75"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="12.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="19.31"/>
@@ -4090,12 +4096,11 @@
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
       <c r="G33" s="28"/>
-      <c r="H33" s="81" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="80"/>
       <c r="B34" s="24"/>
       <c r="C34" s="24"/>
       <c r="D34" s="25"/>
@@ -4104,7 +4109,9 @@
       <c r="G34" s="28"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="80"/>
+      <c r="A35" s="58" t="s">
+        <v>41</v>
+      </c>
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
       <c r="D35" s="25"/>
@@ -4114,7 +4121,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="80" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
@@ -4122,6 +4129,9 @@
       <c r="E36" s="26"/>
       <c r="F36" s="27"/>
       <c r="G36" s="28"/>
+      <c r="H36" s="81" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="80"/>
@@ -4143,7 +4153,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="80" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B39" s="24"/>
       <c r="C39" s="24"/>
@@ -4172,7 +4182,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="80" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B42" s="24"/>
       <c r="C42" s="24"/>
@@ -4201,7 +4211,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="80" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B45" s="24"/>
       <c r="C45" s="24"/>
@@ -4211,6 +4221,7 @@
       <c r="G45" s="28"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="80"/>
       <c r="B46" s="24"/>
       <c r="C46" s="24"/>
       <c r="D46" s="25"/>
@@ -4229,7 +4240,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="80" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="24"/>
@@ -4258,7 +4269,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="80" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B51" s="24"/>
       <c r="C51" s="24"/>
@@ -4287,7 +4298,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="80" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B54" s="24"/>
       <c r="C54" s="24"/>
@@ -4345,7 +4356,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="80" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B60" s="24"/>
       <c r="C60" s="24"/>
@@ -4374,7 +4385,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="80" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B63" s="24"/>
       <c r="C63" s="24"/>
@@ -13110,6 +13121,7 @@
     <hyperlink ref="A20" r:id="rId5" display="deecovana@gmail.com"/>
     <hyperlink ref="A23" r:id="rId6" display="dmytro.cheva@gmail.com"/>
     <hyperlink ref="A26" r:id="rId7" display="dmitry.cheva@gmail.com"/>
+    <hyperlink ref="A35" r:id="rId8" display="wukelan.che@gmail.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13127,7 +13139,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P1055"/>
-  <sheetFormatPr defaultColWidth="12.71484375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.73046875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="0" width="16.63"/>
@@ -13160,11 +13172,11 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="111"/>
       <c r="B2" s="112" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" s="113"/>
       <c r="D2" s="114" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" s="115"/>
       <c r="F2" s="115"/>
@@ -13184,11 +13196,11 @@
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="119"/>
       <c r="B3" s="120" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3" s="121"/>
       <c r="D3" s="122" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E3" s="123"/>
       <c r="F3" s="123"/>
@@ -13246,7 +13258,7 @@
       <c r="B6" s="130"/>
       <c r="C6" s="131"/>
       <c r="D6" s="132" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E6" s="126"/>
       <c r="F6" s="126"/>
@@ -13268,7 +13280,7 @@
       <c r="B7" s="130"/>
       <c r="C7" s="131"/>
       <c r="D7" s="132" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="126"/>
       <c r="F7" s="126"/>
@@ -13328,16 +13340,16 @@
         <v>45058</v>
       </c>
       <c r="B10" s="141" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" s="142"/>
       <c r="D10" s="143" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E10" s="144"/>
       <c r="F10" s="144"/>
       <c r="G10" s="145" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H10" s="145"/>
       <c r="I10" s="146"/>
@@ -13354,11 +13366,11 @@
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="140"/>
       <c r="B11" s="148" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C11" s="142"/>
       <c r="D11" s="143" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" s="144"/>
       <c r="F11" s="144"/>
@@ -13488,16 +13500,16 @@
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="152"/>
       <c r="B18" s="153" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C18" s="154"/>
       <c r="D18" s="155" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E18" s="156"/>
       <c r="F18" s="156"/>
       <c r="G18" s="157" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H18" s="157"/>
       <c r="I18" s="158"/>
@@ -13512,11 +13524,11 @@
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="160"/>
       <c r="B19" s="161" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C19" s="162"/>
       <c r="D19" s="163" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E19" s="164"/>
       <c r="F19" s="164"/>
@@ -13572,7 +13584,7 @@
       <c r="B22" s="170"/>
       <c r="C22" s="171"/>
       <c r="D22" s="172" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E22" s="173"/>
       <c r="F22" s="173"/>
@@ -13580,7 +13592,7 @@
       <c r="H22" s="173"/>
       <c r="I22" s="173"/>
       <c r="J22" s="174" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K22" s="175" t="n">
         <v>100000000</v>
@@ -13596,7 +13608,7 @@
       <c r="B23" s="170"/>
       <c r="C23" s="171"/>
       <c r="D23" s="172" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E23" s="173"/>
       <c r="F23" s="173"/>
@@ -13626,7 +13638,7 @@
       <c r="H24" s="173"/>
       <c r="I24" s="173"/>
       <c r="J24" s="174" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K24" s="175" t="n">
         <v>0</v>
@@ -13664,7 +13676,7 @@
       </c>
       <c r="C26" s="121"/>
       <c r="D26" s="122" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E26" s="123"/>
       <c r="F26" s="123"/>
@@ -13688,7 +13700,7 @@
       </c>
       <c r="C27" s="121"/>
       <c r="D27" s="122" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E27" s="123"/>
       <c r="F27" s="123"/>
@@ -13746,17 +13758,17 @@
       <c r="B30" s="170"/>
       <c r="C30" s="142"/>
       <c r="D30" s="143" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E30" s="144"/>
       <c r="F30" s="144"/>
       <c r="G30" s="184" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H30" s="184"/>
       <c r="I30" s="185"/>
       <c r="J30" s="186" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K30" s="175" t="n">
         <v>34708509</v>
@@ -13772,7 +13784,7 @@
       <c r="B31" s="170"/>
       <c r="C31" s="142"/>
       <c r="D31" s="143" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E31" s="144"/>
       <c r="F31" s="144"/>
@@ -13802,7 +13814,7 @@
       <c r="H32" s="184"/>
       <c r="I32" s="146"/>
       <c r="J32" s="186" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K32" s="175" t="n">
         <v>1000000</v>
@@ -13838,7 +13850,7 @@
       </c>
       <c r="C34" s="121"/>
       <c r="D34" s="122" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E34" s="123"/>
       <c r="F34" s="123"/>
@@ -13862,7 +13874,7 @@
       </c>
       <c r="C35" s="121"/>
       <c r="D35" s="122" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E35" s="123"/>
       <c r="F35" s="123"/>
@@ -13918,7 +13930,7 @@
       <c r="B38" s="170"/>
       <c r="C38" s="171"/>
       <c r="D38" s="172" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E38" s="144"/>
       <c r="F38" s="144"/>
@@ -13926,7 +13938,7 @@
       <c r="H38" s="190"/>
       <c r="I38" s="146"/>
       <c r="J38" s="186" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K38" s="175" t="n">
         <v>58650000</v>
@@ -13942,7 +13954,7 @@
       <c r="B39" s="170"/>
       <c r="C39" s="171"/>
       <c r="D39" s="172" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E39" s="144"/>
       <c r="F39" s="144"/>
@@ -13965,7 +13977,7 @@
       <c r="A40" s="169"/>
       <c r="B40" s="170"/>
       <c r="C40" s="191" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D40" s="143"/>
       <c r="E40" s="144"/>
@@ -13974,7 +13986,7 @@
       <c r="H40" s="190"/>
       <c r="I40" s="146"/>
       <c r="J40" s="186" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K40" s="175" t="n">
         <v>268000</v>
@@ -14014,7 +14026,7 @@
       </c>
       <c r="C42" s="121"/>
       <c r="D42" s="122" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E42" s="122"/>
       <c r="F42" s="123"/>
@@ -14036,7 +14048,7 @@
       <c r="B43" s="198"/>
       <c r="C43" s="121"/>
       <c r="D43" s="122" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E43" s="123"/>
       <c r="F43" s="123"/>
@@ -14094,17 +14106,17 @@
       <c r="B46" s="201"/>
       <c r="C46" s="202"/>
       <c r="D46" s="203" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E46" s="204"/>
       <c r="F46" s="204"/>
       <c r="G46" s="205" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H46" s="205"/>
       <c r="I46" s="206"/>
       <c r="J46" s="207" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K46" s="208" t="n">
         <v>330000</v>
@@ -14120,7 +14132,7 @@
       <c r="B47" s="201"/>
       <c r="C47" s="202"/>
       <c r="D47" s="203" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E47" s="204"/>
       <c r="F47" s="204"/>
@@ -14150,7 +14162,7 @@
       <c r="H48" s="205"/>
       <c r="I48" s="209"/>
       <c r="J48" s="207" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K48" s="208" t="n">
         <v>1000000</v>
@@ -14260,17 +14272,17 @@
       <c r="B54" s="218"/>
       <c r="C54" s="202"/>
       <c r="D54" s="203" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E54" s="204"/>
       <c r="F54" s="204"/>
       <c r="G54" s="219" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H54" s="219"/>
       <c r="I54" s="209"/>
       <c r="J54" s="207" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K54" s="208" t="n">
         <v>660000</v>
@@ -14286,7 +14298,7 @@
       <c r="B55" s="218"/>
       <c r="C55" s="202"/>
       <c r="D55" s="203" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E55" s="204"/>
       <c r="F55" s="204"/>
@@ -14316,7 +14328,7 @@
       <c r="H56" s="219"/>
       <c r="I56" s="209"/>
       <c r="J56" s="207" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K56" s="208" t="n">
         <v>1000000</v>
@@ -14348,11 +14360,11 @@
     <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="220"/>
       <c r="B58" s="221" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C58" s="222"/>
       <c r="D58" s="223" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E58" s="224"/>
       <c r="F58" s="224"/>
@@ -14372,11 +14384,11 @@
     <row r="59" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="227"/>
       <c r="B59" s="228" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C59" s="131"/>
       <c r="D59" s="229" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E59" s="126"/>
       <c r="F59" s="126"/>
@@ -14434,17 +14446,17 @@
       <c r="B62" s="170"/>
       <c r="C62" s="142"/>
       <c r="D62" s="143" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E62" s="144"/>
       <c r="F62" s="144"/>
       <c r="G62" s="184" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H62" s="184"/>
       <c r="I62" s="146"/>
       <c r="J62" s="186" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K62" s="175" t="n">
         <v>104225</v>
@@ -14460,7 +14472,7 @@
       <c r="B63" s="170"/>
       <c r="C63" s="142"/>
       <c r="D63" s="143" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E63" s="144"/>
       <c r="F63" s="144"/>
@@ -14490,7 +14502,7 @@
       <c r="H64" s="184"/>
       <c r="I64" s="146"/>
       <c r="J64" s="186" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K64" s="175" t="n">
         <v>1000000</v>
@@ -14532,11 +14544,11 @@
         <v>7</v>
       </c>
       <c r="H66" s="184" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I66" s="146"/>
       <c r="J66" s="186" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K66" s="175" t="n">
         <v>520000000</v>
@@ -14575,7 +14587,7 @@
       <c r="A68" s="231"/>
       <c r="B68" s="170"/>
       <c r="C68" s="191" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D68" s="144"/>
       <c r="E68" s="144"/>
@@ -14584,7 +14596,7 @@
       <c r="H68" s="184"/>
       <c r="I68" s="146"/>
       <c r="J68" s="186" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K68" s="175" t="n">
         <v>386000</v>
@@ -14601,7 +14613,7 @@
       </c>
       <c r="B69" s="170"/>
       <c r="C69" s="191" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D69" s="144"/>
       <c r="E69" s="144"/>
@@ -14627,14 +14639,14 @@
       <c r="E70" s="238"/>
       <c r="F70" s="238"/>
       <c r="G70" s="239" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H70" s="240" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I70" s="241"/>
       <c r="J70" s="242" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K70" s="243" t="n">
         <v>300000</v>
@@ -14680,7 +14692,7 @@
       <c r="H72" s="240"/>
       <c r="I72" s="146"/>
       <c r="J72" s="186" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K72" s="175" t="n">
         <v>1000000</v>
@@ -14693,7 +14705,7 @@
     </row>
     <row r="73" customFormat="false" ht="44.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="245" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B73" s="177"/>
       <c r="C73" s="187"/>
@@ -14753,7 +14765,7 @@
         <v>11</v>
       </c>
       <c r="C76" s="229" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D76" s="229"/>
       <c r="E76" s="126"/>
@@ -14772,7 +14784,7 @@
     <row r="77" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="246"/>
       <c r="B77" s="249" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C77" s="131"/>
       <c r="D77" s="126"/>
@@ -14812,7 +14824,7 @@
     <row r="79" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="246"/>
       <c r="B79" s="250" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C79" s="131"/>
       <c r="D79" s="126"/>
@@ -14832,10 +14844,10 @@
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="246"/>
       <c r="B80" s="249" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C80" s="229" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D80" s="126"/>
       <c r="E80" s="126"/>
@@ -14872,7 +14884,7 @@
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="246"/>
       <c r="B82" s="248" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C82" s="229"/>
       <c r="D82" s="126"/>
@@ -14892,7 +14904,7 @@
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="246"/>
       <c r="B83" s="249" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C83" s="229"/>
       <c r="D83" s="126"/>
@@ -14912,7 +14924,7 @@
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="246"/>
       <c r="B84" s="248" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C84" s="229"/>
       <c r="D84" s="126"/>
@@ -14932,7 +14944,7 @@
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="246"/>
       <c r="B85" s="250" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C85" s="229"/>
       <c r="D85" s="126"/>
@@ -14952,10 +14964,10 @@
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="246"/>
       <c r="B86" s="249" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C86" s="229" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D86" s="126"/>
       <c r="E86" s="126"/>
@@ -15010,7 +15022,7 @@
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="246"/>
       <c r="B89" s="248" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C89" s="229"/>
       <c r="D89" s="126"/>
@@ -15030,7 +15042,7 @@
     <row r="90" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="246"/>
       <c r="B90" s="251" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C90" s="131"/>
       <c r="D90" s="126"/>
@@ -15050,7 +15062,7 @@
     <row r="91" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="246"/>
       <c r="B91" s="251" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C91" s="131"/>
       <c r="D91" s="126"/>
@@ -15070,7 +15082,7 @@
     <row r="92" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="246"/>
       <c r="B92" s="250" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C92" s="131"/>
       <c r="D92" s="126"/>
@@ -15090,10 +15102,10 @@
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="246"/>
       <c r="B93" s="249" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C93" s="229" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D93" s="126"/>
       <c r="E93" s="126"/>
@@ -15187,7 +15199,7 @@
         <v>23</v>
       </c>
       <c r="C98" s="143" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D98" s="144"/>
       <c r="E98" s="144"/>
@@ -15206,7 +15218,7 @@
     <row r="99" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="252"/>
       <c r="B99" s="255" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C99" s="142"/>
       <c r="D99" s="144"/>
@@ -15249,7 +15261,7 @@
         <v>25</v>
       </c>
       <c r="C101" s="143" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D101" s="144"/>
       <c r="E101" s="144"/>
@@ -15324,7 +15336,7 @@
     <row r="105" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="246"/>
       <c r="B105" s="251" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C105" s="131"/>
       <c r="D105" s="126"/>
@@ -15367,7 +15379,7 @@
         <v>9</v>
       </c>
       <c r="C107" s="229" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D107" s="126"/>
       <c r="E107" s="126"/>
@@ -15422,7 +15434,7 @@
     <row r="110" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="258"/>
       <c r="B110" s="251" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C110" s="131"/>
       <c r="D110" s="126"/>
@@ -15521,7 +15533,7 @@
       <c r="G115" s="126"/>
       <c r="H115" s="126"/>
       <c r="I115" s="262" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J115" s="263"/>
       <c r="K115" s="263"/>
@@ -15581,7 +15593,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="267" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L118" s="126"/>
       <c r="M118" s="126"/>
@@ -15603,7 +15615,7 @@
         <v>7</v>
       </c>
       <c r="K119" s="267" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L119" s="126"/>
       <c r="M119" s="126"/>
@@ -15622,7 +15634,7 @@
       <c r="H120" s="126"/>
       <c r="I120" s="268"/>
       <c r="J120" s="270" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K120" s="260"/>
       <c r="L120" s="126"/>
@@ -15642,7 +15654,7 @@
       <c r="H121" s="126"/>
       <c r="I121" s="268"/>
       <c r="J121" s="271" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K121" s="260"/>
       <c r="L121" s="126"/>
